--- a/artfynd/A 33841-2023 artfynd.xlsx
+++ b/artfynd/A 33841-2023 artfynd.xlsx
@@ -1001,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122969836</v>
+        <v>122973309</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481538</v>
+        <v>481568</v>
       </c>
       <c r="R5" t="n">
-        <v>6790506</v>
+        <v>6790545</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122970211</v>
+        <v>122969836</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481559</v>
+        <v>481538</v>
       </c>
       <c r="R6" t="n">
-        <v>6790521</v>
+        <v>6790506</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,7 +1225,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122973309</v>
+        <v>122970211</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481568</v>
+        <v>481559</v>
       </c>
       <c r="R7" t="n">
-        <v>6790545</v>
+        <v>6790521</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2519,7 +2519,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122970352</v>
+        <v>122970156</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481566</v>
+        <v>481546</v>
       </c>
       <c r="R19" t="n">
-        <v>6790511</v>
+        <v>6790501</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2631,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122970156</v>
+        <v>122970092</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>78792</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2643,25 +2643,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481546</v>
+        <v>481532</v>
       </c>
       <c r="R20" t="n">
-        <v>6790501</v>
+        <v>6790516</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2743,10 +2743,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122970092</v>
+        <v>122970352</v>
       </c>
       <c r="B21" t="n">
-        <v>78792</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2755,25 +2755,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2783,10 +2783,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481532</v>
+        <v>481566</v>
       </c>
       <c r="R21" t="n">
-        <v>6790516</v>
+        <v>6790511</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122973048</v>
+        <v>122972843</v>
       </c>
       <c r="B24" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3086,25 +3086,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481694</v>
+        <v>481748</v>
       </c>
       <c r="R24" t="n">
-        <v>6790479</v>
+        <v>6790465</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3150,11 +3150,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Mindre märgborre på låga.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3181,10 +3176,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122972843</v>
+        <v>122973048</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3193,25 +3188,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3221,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481748</v>
+        <v>481694</v>
       </c>
       <c r="R25" t="n">
-        <v>6790465</v>
+        <v>6790479</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3257,6 +3252,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Mindre märgborre på låga.</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 33841-2023 artfynd.xlsx
+++ b/artfynd/A 33841-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122969887</v>
+        <v>122970352</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481534</v>
+        <v>481566</v>
       </c>
       <c r="R2" t="n">
-        <v>6790501</v>
+        <v>6790511</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122970062</v>
+        <v>122970166</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481533</v>
+        <v>481546</v>
       </c>
       <c r="R3" t="n">
-        <v>6790513</v>
+        <v>6790501</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122973297</v>
+        <v>122973371</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -935,17 +940,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481575</v>
+        <v>481551</v>
       </c>
       <c r="R4" t="n">
-        <v>6790530</v>
+        <v>6790539</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,9 +977,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,19 +1004,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122973309</v>
+        <v>122969887</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1041,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481568</v>
+        <v>481534</v>
       </c>
       <c r="R5" t="n">
-        <v>6790545</v>
+        <v>6790501</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1076,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122969836</v>
+        <v>122973404</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1149,17 +1164,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481538</v>
+        <v>481525</v>
       </c>
       <c r="R6" t="n">
-        <v>6790506</v>
+        <v>6790521</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1186,19 +1201,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,19 +1218,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122970211</v>
+        <v>122973389</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1265,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481559</v>
+        <v>481565</v>
       </c>
       <c r="R7" t="n">
-        <v>6790521</v>
+        <v>6790545</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1300,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122973404</v>
+        <v>122969981</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>78767</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,16 +1358,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1373,14 +1378,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481525</v>
+        <v>481565</v>
       </c>
       <c r="R8" t="n">
-        <v>6790521</v>
+        <v>6790484</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,6 +1418,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Garnlav runt omkring mig i en radie av 40 meter.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,7 +1449,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122973389</v>
+        <v>122970152</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1475,17 +1485,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481565</v>
+        <v>481577</v>
       </c>
       <c r="R9" t="n">
-        <v>6790545</v>
+        <v>6790481</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,19 +1522,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,22 +1539,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122970166</v>
+        <v>122970062</v>
       </c>
       <c r="B10" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1563,43 +1563,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481546</v>
+        <v>481533</v>
       </c>
       <c r="R10" t="n">
-        <v>6790501</v>
+        <v>6790513</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1631,7 +1626,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1641,7 +1636,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,7 +1663,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122970152</v>
+        <v>122970156</v>
       </c>
       <c r="B11" t="n">
         <v>78766</v>
@@ -1704,17 +1699,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481577</v>
+        <v>481546</v>
       </c>
       <c r="R11" t="n">
-        <v>6790481</v>
+        <v>6790501</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1741,9 +1736,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,19 +1763,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122970196</v>
+        <v>122969601</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1810,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481598</v>
+        <v>481528</v>
       </c>
       <c r="R12" t="n">
-        <v>6790481</v>
+        <v>6790490</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,7 +1877,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122973371</v>
+        <v>122970196</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1908,17 +1913,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481551</v>
+        <v>481598</v>
       </c>
       <c r="R13" t="n">
-        <v>6790539</v>
+        <v>6790481</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1945,19 +1950,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,19 +1967,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122969800</v>
+        <v>122970092</v>
       </c>
       <c r="B14" t="n">
         <v>78792</v>
@@ -2024,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481538</v>
+        <v>481532</v>
       </c>
       <c r="R14" t="n">
-        <v>6790506</v>
+        <v>6790516</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2059,7 +2054,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,7 +2064,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,10 +2091,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122969981</v>
+        <v>122970211</v>
       </c>
       <c r="B15" t="n">
-        <v>78767</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2112,16 +2107,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2132,17 +2127,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481565</v>
+        <v>481559</v>
       </c>
       <c r="R15" t="n">
-        <v>6790484</v>
+        <v>6790521</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2169,14 +2164,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Garnlav runt omkring mig i en radie av 40 meter.</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,22 +2191,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122969601</v>
+        <v>122969848</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>78767</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2219,16 +2219,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2243,10 +2243,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481528</v>
+        <v>481544</v>
       </c>
       <c r="R16" t="n">
-        <v>6790490</v>
+        <v>6790494</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2279,6 +2279,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Torraka i bakgrunden.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,10 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122970333</v>
+        <v>122969800</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>78792</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2317,41 +2322,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481622</v>
+        <v>481538</v>
       </c>
       <c r="R17" t="n">
-        <v>6790484</v>
+        <v>6790506</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2378,14 +2383,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbilder.</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2400,22 +2410,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122969848</v>
+        <v>122973297</v>
       </c>
       <c r="B18" t="n">
-        <v>78767</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2428,16 +2438,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2448,14 +2458,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481544</v>
+        <v>481575</v>
       </c>
       <c r="R18" t="n">
-        <v>6790494</v>
+        <v>6790530</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2488,11 +2498,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Torraka i bakgrunden.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2519,7 +2524,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122970156</v>
+        <v>122969836</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2559,10 +2564,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481546</v>
+        <v>481538</v>
       </c>
       <c r="R19" t="n">
-        <v>6790501</v>
+        <v>6790506</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2594,7 +2599,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2604,7 +2609,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2631,10 +2636,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122970092</v>
+        <v>122970333</v>
       </c>
       <c r="B20" t="n">
-        <v>78792</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2643,41 +2648,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481532</v>
+        <v>481622</v>
       </c>
       <c r="R20" t="n">
-        <v>6790516</v>
+        <v>6790484</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2704,19 +2709,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:05</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbilder.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2731,19 +2731,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122970352</v>
+        <v>122973309</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -2783,10 +2783,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481566</v>
+        <v>481568</v>
       </c>
       <c r="R21" t="n">
-        <v>6790511</v>
+        <v>6790545</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,10 +2855,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122970459</v>
+        <v>122973048</v>
       </c>
       <c r="B22" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2867,38 +2867,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481658</v>
+        <v>481694</v>
       </c>
       <c r="R22" t="n">
-        <v>6790493</v>
+        <v>6790479</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Miljöbilder och spillkråka.</t>
+          <t>Mindre märgborre på låga.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2962,7 +2962,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122972089</v>
+        <v>122972633</v>
       </c>
       <c r="B23" t="n">
         <v>78766</v>
@@ -2998,17 +2998,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481695</v>
+        <v>481748</v>
       </c>
       <c r="R23" t="n">
-        <v>6790593</v>
+        <v>6790465</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3035,19 +3035,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3062,22 +3052,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122972843</v>
+        <v>122971698</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3086,38 +3076,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481748</v>
+        <v>481661</v>
       </c>
       <c r="R24" t="n">
-        <v>6790465</v>
+        <v>6790503</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3176,10 +3166,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122973048</v>
+        <v>122971770</v>
       </c>
       <c r="B25" t="n">
-        <v>8441</v>
+        <v>78792</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3192,37 +3182,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6434</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481694</v>
+        <v>481677</v>
       </c>
       <c r="R25" t="n">
-        <v>6790479</v>
+        <v>6790565</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3249,14 +3239,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Mindre märgborre på låga.</t>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3271,22 +3266,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122971431</v>
+        <v>122971852</v>
       </c>
       <c r="B26" t="n">
-        <v>78502</v>
+        <v>8441</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3295,38 +3290,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481658</v>
+        <v>481678</v>
       </c>
       <c r="R26" t="n">
-        <v>6790494</v>
+        <v>6790570</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3395,10 +3395,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122971698</v>
+        <v>122972089</v>
       </c>
       <c r="B27" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3407,41 +3407,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481661</v>
+        <v>481695</v>
       </c>
       <c r="R27" t="n">
-        <v>6790503</v>
+        <v>6790593</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3468,9 +3468,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3485,19 +3495,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122971852</v>
+        <v>122972025</v>
       </c>
       <c r="B28" t="n">
         <v>8441</v>
@@ -3542,10 +3552,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481678</v>
+        <v>481687</v>
       </c>
       <c r="R28" t="n">
-        <v>6790570</v>
+        <v>6790643</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -3577,7 +3587,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3587,7 +3597,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3614,10 +3624,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122971770</v>
+        <v>122970459</v>
       </c>
       <c r="B29" t="n">
-        <v>78792</v>
+        <v>57494</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3626,41 +3636,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481677</v>
+        <v>481658</v>
       </c>
       <c r="R29" t="n">
-        <v>6790565</v>
+        <v>6790493</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3687,19 +3697,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:53</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Miljöbilder och spillkråka.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3714,22 +3719,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122972025</v>
+        <v>122972148</v>
       </c>
       <c r="B30" t="n">
-        <v>8441</v>
+        <v>78767</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3738,46 +3743,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>230405</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481687</v>
+        <v>481755</v>
       </c>
       <c r="R30" t="n">
-        <v>6790643</v>
+        <v>6790500</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3804,19 +3804,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:59</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3831,22 +3826,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122972148</v>
+        <v>122971431</v>
       </c>
       <c r="B31" t="n">
-        <v>78767</v>
+        <v>78502</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3859,37 +3854,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>230405</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481755</v>
+        <v>481658</v>
       </c>
       <c r="R31" t="n">
-        <v>6790500</v>
+        <v>6790494</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3916,14 +3911,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbild.</t>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3938,12 +3938,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 33841-2023 artfynd.xlsx
+++ b/artfynd/A 33841-2023 artfynd.xlsx
@@ -2962,10 +2962,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122972633</v>
+        <v>122971698</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2974,38 +2974,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481748</v>
+        <v>481661</v>
       </c>
       <c r="R23" t="n">
-        <v>6790465</v>
+        <v>6790503</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3064,10 +3064,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122971698</v>
+        <v>122971770</v>
       </c>
       <c r="B24" t="n">
-        <v>8441</v>
+        <v>78792</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3080,37 +3080,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6434</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481661</v>
+        <v>481677</v>
       </c>
       <c r="R24" t="n">
-        <v>6790503</v>
+        <v>6790565</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3137,9 +3137,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3154,22 +3164,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122971770</v>
+        <v>122972843</v>
       </c>
       <c r="B25" t="n">
-        <v>78792</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3178,41 +3188,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481677</v>
+        <v>481748</v>
       </c>
       <c r="R25" t="n">
-        <v>6790565</v>
+        <v>6790465</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3239,19 +3249,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3266,12 +3266,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3395,10 +3395,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122972089</v>
+        <v>122972025</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3407,38 +3407,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481695</v>
+        <v>481687</v>
       </c>
       <c r="R27" t="n">
-        <v>6790593</v>
+        <v>6790643</v>
       </c>
       <c r="S27" t="n">
         <v>9</v>
@@ -3470,7 +3475,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3480,7 +3485,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3507,10 +3512,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122972025</v>
+        <v>122972089</v>
       </c>
       <c r="B28" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3519,43 +3524,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481687</v>
+        <v>481695</v>
       </c>
       <c r="R28" t="n">
-        <v>6790643</v>
+        <v>6790593</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 33841-2023 artfynd.xlsx
+++ b/artfynd/A 33841-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122970352</v>
+        <v>122969601</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481566</v>
+        <v>481528</v>
       </c>
       <c r="R2" t="n">
-        <v>6790511</v>
+        <v>6790490</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +748,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122970166</v>
+        <v>122970352</v>
       </c>
       <c r="B3" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481546</v>
+        <v>481566</v>
       </c>
       <c r="R3" t="n">
-        <v>6790501</v>
+        <v>6790511</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -867,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122973371</v>
+        <v>122969848</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>78767</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,16 +905,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -940,17 +925,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481551</v>
+        <v>481544</v>
       </c>
       <c r="R4" t="n">
-        <v>6790539</v>
+        <v>6790494</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,19 +962,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:42</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Torraka i bakgrunden.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,19 +984,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122969887</v>
+        <v>122973371</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1056,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481534</v>
+        <v>481551</v>
       </c>
       <c r="R5" t="n">
-        <v>6790501</v>
+        <v>6790539</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1091,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122973404</v>
+        <v>122969981</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>78767</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,16 +1124,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1164,14 +1144,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481525</v>
+        <v>481565</v>
       </c>
       <c r="R6" t="n">
-        <v>6790521</v>
+        <v>6790484</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,6 +1184,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Garnlav runt omkring mig i en radie av 40 meter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122973389</v>
+        <v>122973297</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1266,17 +1251,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481565</v>
+        <v>481575</v>
       </c>
       <c r="R7" t="n">
-        <v>6790545</v>
+        <v>6790530</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,19 +1288,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,22 +1305,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122969981</v>
+        <v>122970092</v>
       </c>
       <c r="B8" t="n">
-        <v>78767</v>
+        <v>78792</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,41 +1329,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>230405</v>
+        <v>6434</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481565</v>
+        <v>481532</v>
       </c>
       <c r="R8" t="n">
-        <v>6790484</v>
+        <v>6790516</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1415,14 +1390,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Garnlav runt omkring mig i en radie av 40 meter.</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,19 +1417,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122970152</v>
+        <v>122973309</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1485,17 +1465,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481577</v>
+        <v>481568</v>
       </c>
       <c r="R9" t="n">
-        <v>6790481</v>
+        <v>6790545</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1522,9 +1502,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,19 +1529,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122970062</v>
+        <v>122973389</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1591,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481533</v>
+        <v>481565</v>
       </c>
       <c r="R10" t="n">
-        <v>6790513</v>
+        <v>6790545</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1626,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1636,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,7 +1653,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122970156</v>
+        <v>122970196</v>
       </c>
       <c r="B11" t="n">
         <v>78766</v>
@@ -1699,17 +1689,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481546</v>
+        <v>481598</v>
       </c>
       <c r="R11" t="n">
-        <v>6790501</v>
+        <v>6790481</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1736,19 +1726,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,19 +1743,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122969601</v>
+        <v>122973404</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1811,14 +1791,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481528</v>
+        <v>481525</v>
       </c>
       <c r="R12" t="n">
-        <v>6790490</v>
+        <v>6790521</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,7 +1857,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122970196</v>
+        <v>122969836</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1913,17 +1893,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481598</v>
+        <v>481538</v>
       </c>
       <c r="R13" t="n">
-        <v>6790481</v>
+        <v>6790506</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1950,9 +1930,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,22 +1957,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122970092</v>
+        <v>122970152</v>
       </c>
       <c r="B14" t="n">
-        <v>78792</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1991,41 +1981,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481532</v>
+        <v>481577</v>
       </c>
       <c r="R14" t="n">
-        <v>6790516</v>
+        <v>6790481</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2052,19 +2042,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,19 +2059,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122970211</v>
+        <v>122970062</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2131,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481559</v>
+        <v>481533</v>
       </c>
       <c r="R15" t="n">
-        <v>6790521</v>
+        <v>6790513</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2166,7 +2146,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2176,7 +2156,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122969848</v>
+        <v>122969887</v>
       </c>
       <c r="B16" t="n">
-        <v>78767</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2219,16 +2199,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2239,17 +2219,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481544</v>
+        <v>481534</v>
       </c>
       <c r="R16" t="n">
-        <v>6790494</v>
+        <v>6790501</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2276,14 +2256,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Torraka i bakgrunden.</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2298,22 +2283,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122969800</v>
+        <v>122970156</v>
       </c>
       <c r="B17" t="n">
-        <v>78792</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2322,25 +2307,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2350,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481538</v>
+        <v>481546</v>
       </c>
       <c r="R17" t="n">
-        <v>6790506</v>
+        <v>6790501</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2385,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2395,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2422,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122973297</v>
+        <v>122969800</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>78792</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2434,41 +2419,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481575</v>
+        <v>481538</v>
       </c>
       <c r="R18" t="n">
-        <v>6790530</v>
+        <v>6790506</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2495,9 +2480,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2512,19 +2507,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122969836</v>
+        <v>122970333</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2560,17 +2555,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481538</v>
+        <v>481622</v>
       </c>
       <c r="R19" t="n">
-        <v>6790506</v>
+        <v>6790484</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2597,19 +2592,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:00</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbilder.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2624,19 +2614,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122970333</v>
+        <v>122970211</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -2672,17 +2662,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481622</v>
+        <v>481559</v>
       </c>
       <c r="R20" t="n">
-        <v>6790484</v>
+        <v>6790521</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2709,14 +2699,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbilder.</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2731,22 +2726,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122973309</v>
+        <v>122970166</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2755,38 +2750,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481568</v>
+        <v>481546</v>
       </c>
       <c r="R21" t="n">
-        <v>6790545</v>
+        <v>6790501</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,10 +2855,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122973048</v>
+        <v>122972843</v>
       </c>
       <c r="B22" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2867,25 +2867,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2895,10 +2895,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481694</v>
+        <v>481748</v>
       </c>
       <c r="R22" t="n">
-        <v>6790479</v>
+        <v>6790465</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2931,11 +2931,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Mindre märgborre på låga.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2962,7 +2957,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122971698</v>
+        <v>122971852</v>
       </c>
       <c r="B23" t="n">
         <v>8441</v>
@@ -2996,19 +2991,24 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481661</v>
+        <v>481678</v>
       </c>
       <c r="R23" t="n">
-        <v>6790503</v>
+        <v>6790570</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3035,9 +3035,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3052,12 +3062,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3176,10 +3186,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122972843</v>
+        <v>122972148</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>78767</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3192,16 +3202,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3216,10 +3226,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481748</v>
+        <v>481755</v>
       </c>
       <c r="R25" t="n">
-        <v>6790465</v>
+        <v>6790500</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3252,6 +3262,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3278,10 +3293,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122971852</v>
+        <v>122971431</v>
       </c>
       <c r="B26" t="n">
-        <v>8441</v>
+        <v>78502</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3290,43 +3305,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481678</v>
+        <v>481658</v>
       </c>
       <c r="R26" t="n">
-        <v>6790570</v>
+        <v>6790494</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -3358,7 +3368,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3368,7 +3378,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3395,7 +3405,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122972025</v>
+        <v>122973048</v>
       </c>
       <c r="B27" t="n">
         <v>8441</v>
@@ -3429,24 +3439,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481687</v>
+        <v>481694</v>
       </c>
       <c r="R27" t="n">
-        <v>6790643</v>
+        <v>6790479</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3473,19 +3478,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:59</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Mindre märgborre på låga.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3500,22 +3500,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122972089</v>
+        <v>122972025</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3524,38 +3524,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481695</v>
+        <v>481687</v>
       </c>
       <c r="R28" t="n">
-        <v>6790593</v>
+        <v>6790643</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -3587,7 +3592,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3597,7 +3602,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3624,10 +3629,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122970459</v>
+        <v>122972089</v>
       </c>
       <c r="B29" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3640,37 +3645,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481658</v>
+        <v>481695</v>
       </c>
       <c r="R29" t="n">
-        <v>6790493</v>
+        <v>6790593</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3697,14 +3702,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Miljöbilder och spillkråka.</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3719,22 +3729,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122972148</v>
+        <v>122971698</v>
       </c>
       <c r="B30" t="n">
-        <v>78767</v>
+        <v>8441</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3743,38 +3753,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>230405</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481755</v>
+        <v>481661</v>
       </c>
       <c r="R30" t="n">
-        <v>6790500</v>
+        <v>6790503</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3807,11 +3817,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3838,10 +3843,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122971431</v>
+        <v>122970459</v>
       </c>
       <c r="B31" t="n">
-        <v>78502</v>
+        <v>57494</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3854,37 +3859,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
         <v>481658</v>
       </c>
       <c r="R31" t="n">
-        <v>6790494</v>
+        <v>6790493</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3911,19 +3916,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:44</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Miljöbilder och spillkråka.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3938,12 +3938,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 33841-2023 artfynd.xlsx
+++ b/artfynd/A 33841-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122969601</v>
+        <v>122970352</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481528</v>
+        <v>481566</v>
       </c>
       <c r="R2" t="n">
-        <v>6790490</v>
+        <v>6790511</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +748,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,19 +775,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122970352</v>
+        <v>122969601</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -813,17 +823,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481566</v>
+        <v>481528</v>
       </c>
       <c r="R3" t="n">
-        <v>6790511</v>
+        <v>6790490</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,19 +860,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,12 +877,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -2855,10 +2855,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122972843</v>
+        <v>122971852</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2867,41 +2867,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481748</v>
+        <v>481678</v>
       </c>
       <c r="R22" t="n">
-        <v>6790465</v>
+        <v>6790570</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2928,9 +2933,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2945,22 +2960,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122971852</v>
+        <v>122972843</v>
       </c>
       <c r="B23" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2969,46 +2984,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481678</v>
+        <v>481748</v>
       </c>
       <c r="R23" t="n">
-        <v>6790570</v>
+        <v>6790465</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3035,19 +3045,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3062,12 +3062,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 33841-2023 artfynd.xlsx
+++ b/artfynd/A 33841-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122970352</v>
+        <v>122970196</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481566</v>
+        <v>481598</v>
       </c>
       <c r="R2" t="n">
-        <v>6790511</v>
+        <v>6790481</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +748,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122969601</v>
+        <v>122970062</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -823,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481528</v>
+        <v>481533</v>
       </c>
       <c r="R3" t="n">
-        <v>6790490</v>
+        <v>6790513</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,9 +850,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122969848</v>
+        <v>122970211</v>
       </c>
       <c r="B4" t="n">
-        <v>78767</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,16 +905,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -925,17 +925,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481544</v>
+        <v>481559</v>
       </c>
       <c r="R4" t="n">
-        <v>6790494</v>
+        <v>6790521</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -962,14 +962,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Torraka i bakgrunden.</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,19 +989,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122973371</v>
+        <v>122973389</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1036,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481551</v>
+        <v>481565</v>
       </c>
       <c r="R5" t="n">
-        <v>6790539</v>
+        <v>6790545</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122969981</v>
+        <v>122970092</v>
       </c>
       <c r="B6" t="n">
-        <v>78767</v>
+        <v>78790</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,41 +1125,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230405</v>
+        <v>6434</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481565</v>
+        <v>481532</v>
       </c>
       <c r="R6" t="n">
-        <v>6790484</v>
+        <v>6790516</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1181,14 +1186,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Garnlav runt omkring mig i en radie av 40 meter.</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,19 +1213,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122973297</v>
+        <v>122969836</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1251,17 +1261,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481575</v>
+        <v>481538</v>
       </c>
       <c r="R7" t="n">
-        <v>6790530</v>
+        <v>6790506</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1288,9 +1298,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,22 +1325,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122970092</v>
+        <v>122970152</v>
       </c>
       <c r="B8" t="n">
-        <v>78792</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,41 +1349,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481532</v>
+        <v>481577</v>
       </c>
       <c r="R8" t="n">
-        <v>6790516</v>
+        <v>6790481</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1390,19 +1410,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,19 +1427,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122973309</v>
+        <v>122973297</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1465,17 +1475,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481568</v>
+        <v>481575</v>
       </c>
       <c r="R9" t="n">
-        <v>6790545</v>
+        <v>6790530</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1502,19 +1512,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,19 +1529,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122973389</v>
+        <v>122973309</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481565</v>
+        <v>481568</v>
       </c>
       <c r="R10" t="n">
         <v>6790545</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,7 +1653,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122970196</v>
+        <v>122970352</v>
       </c>
       <c r="B11" t="n">
         <v>78766</v>
@@ -1689,17 +1689,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481598</v>
+        <v>481566</v>
       </c>
       <c r="R11" t="n">
-        <v>6790481</v>
+        <v>6790511</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1726,9 +1726,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,22 +1753,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122973404</v>
+        <v>122969981</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>78767</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,16 +1781,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1791,14 +1801,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481525</v>
+        <v>481565</v>
       </c>
       <c r="R12" t="n">
-        <v>6790521</v>
+        <v>6790484</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,6 +1841,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Garnlav runt omkring mig i en radie av 40 meter.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122969836</v>
+        <v>122969848</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>78767</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,16 +1888,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1893,17 +1908,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481538</v>
+        <v>481544</v>
       </c>
       <c r="R13" t="n">
-        <v>6790506</v>
+        <v>6790494</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1930,19 +1945,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:00</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Torraka i bakgrunden.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,22 +1967,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122970152</v>
+        <v>122970166</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1981,41 +1991,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481577</v>
+        <v>481546</v>
       </c>
       <c r="R14" t="n">
-        <v>6790481</v>
+        <v>6790501</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2042,9 +2057,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2059,22 +2084,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122970062</v>
+        <v>122969800</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>78790</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2083,25 +2108,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,10 +2136,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481533</v>
+        <v>481538</v>
       </c>
       <c r="R15" t="n">
-        <v>6790513</v>
+        <v>6790506</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2146,7 +2171,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2156,7 +2181,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,7 +2208,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122969887</v>
+        <v>122973404</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2219,17 +2244,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481534</v>
+        <v>481525</v>
       </c>
       <c r="R16" t="n">
-        <v>6790501</v>
+        <v>6790521</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2256,19 +2281,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2283,12 +2298,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2407,10 +2422,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122969800</v>
+        <v>122970333</v>
       </c>
       <c r="B18" t="n">
-        <v>78792</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2419,41 +2434,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481538</v>
+        <v>481622</v>
       </c>
       <c r="R18" t="n">
-        <v>6790506</v>
+        <v>6790484</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2480,19 +2495,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:00</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbilder.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2507,19 +2517,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122970333</v>
+        <v>122973371</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2555,17 +2565,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481622</v>
+        <v>481551</v>
       </c>
       <c r="R19" t="n">
-        <v>6790484</v>
+        <v>6790539</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2592,14 +2602,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbilder.</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2614,19 +2629,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122970211</v>
+        <v>122969601</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -2662,17 +2677,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481559</v>
+        <v>481528</v>
       </c>
       <c r="R20" t="n">
-        <v>6790521</v>
+        <v>6790490</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2699,19 +2714,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2726,22 +2731,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122970166</v>
+        <v>122969887</v>
       </c>
       <c r="B21" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2750,40 +2755,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481546</v>
+        <v>481534</v>
       </c>
       <c r="R21" t="n">
         <v>6790501</v>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,10 +2855,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122971852</v>
+        <v>122971770</v>
       </c>
       <c r="B22" t="n">
-        <v>8441</v>
+        <v>78790</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2871,39 +2871,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6434</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481678</v>
+        <v>481677</v>
       </c>
       <c r="R22" t="n">
-        <v>6790570</v>
+        <v>6790565</v>
       </c>
       <c r="S22" t="n">
         <v>9</v>
@@ -2935,7 +2930,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2945,7 +2940,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2972,10 +2967,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122972843</v>
+        <v>122971852</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2984,41 +2979,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481748</v>
+        <v>481678</v>
       </c>
       <c r="R23" t="n">
-        <v>6790465</v>
+        <v>6790570</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3045,9 +3045,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3062,22 +3072,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122971770</v>
+        <v>122972843</v>
       </c>
       <c r="B24" t="n">
-        <v>78792</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3086,41 +3096,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481677</v>
+        <v>481748</v>
       </c>
       <c r="R24" t="n">
-        <v>6790565</v>
+        <v>6790465</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3147,19 +3157,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3174,22 +3174,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122972148</v>
+        <v>122971431</v>
       </c>
       <c r="B25" t="n">
-        <v>78767</v>
+        <v>78502</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3202,37 +3202,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>230405</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481755</v>
+        <v>481658</v>
       </c>
       <c r="R25" t="n">
-        <v>6790500</v>
+        <v>6790494</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3259,14 +3259,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbild.</t>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3281,22 +3286,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122971431</v>
+        <v>122970459</v>
       </c>
       <c r="B26" t="n">
-        <v>78502</v>
+        <v>57494</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3309,37 +3314,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
         <v>481658</v>
       </c>
       <c r="R26" t="n">
-        <v>6790494</v>
+        <v>6790493</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3366,19 +3371,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:44</t>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Miljöbilder och spillkråka.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3393,12 +3393,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3512,10 +3512,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122972025</v>
+        <v>122972089</v>
       </c>
       <c r="B28" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3524,43 +3524,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481687</v>
+        <v>481695</v>
       </c>
       <c r="R28" t="n">
-        <v>6790643</v>
+        <v>6790593</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -3592,7 +3587,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3602,7 +3597,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3629,10 +3624,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122972089</v>
+        <v>122972148</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>78767</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3645,16 +3640,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3665,17 +3660,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481695</v>
+        <v>481755</v>
       </c>
       <c r="R29" t="n">
-        <v>6790593</v>
+        <v>6790500</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3702,19 +3697,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>15:02</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3729,19 +3719,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122971698</v>
+        <v>122972025</v>
       </c>
       <c r="B30" t="n">
         <v>8441</v>
@@ -3775,19 +3765,24 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481661</v>
+        <v>481687</v>
       </c>
       <c r="R30" t="n">
-        <v>6790503</v>
+        <v>6790643</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3814,9 +3809,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3831,22 +3836,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122970459</v>
+        <v>122971698</v>
       </c>
       <c r="B31" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3855,25 +3860,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3883,10 +3888,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481658</v>
+        <v>481661</v>
       </c>
       <c r="R31" t="n">
-        <v>6790493</v>
+        <v>6790503</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3919,11 +3924,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Miljöbilder och spillkråka.</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 33841-2023 artfynd.xlsx
+++ b/artfynd/A 33841-2023 artfynd.xlsx
@@ -1979,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122970166</v>
+        <v>122969800</v>
       </c>
       <c r="B14" t="n">
-        <v>8441</v>
+        <v>78790</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,39 +1995,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6434</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481546</v>
+        <v>481538</v>
       </c>
       <c r="R14" t="n">
-        <v>6790501</v>
+        <v>6790506</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2059,7 +2054,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,7 +2064,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,10 +2091,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122969800</v>
+        <v>122970166</v>
       </c>
       <c r="B15" t="n">
-        <v>78790</v>
+        <v>8441</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2112,34 +2107,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6434</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481538</v>
+        <v>481546</v>
       </c>
       <c r="R15" t="n">
-        <v>6790506</v>
+        <v>6790501</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 33841-2023 artfynd.xlsx
+++ b/artfynd/A 33841-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122970196</v>
+        <v>122969800</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>78790</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481598</v>
+        <v>481538</v>
       </c>
       <c r="R2" t="n">
-        <v>6790481</v>
+        <v>6790506</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +748,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,19 +775,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122970062</v>
+        <v>122969887</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -817,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481533</v>
+        <v>481534</v>
       </c>
       <c r="R3" t="n">
-        <v>6790513</v>
+        <v>6790501</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -852,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122970211</v>
+        <v>122973404</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -925,17 +935,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481559</v>
+        <v>481525</v>
       </c>
       <c r="R4" t="n">
         <v>6790521</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -962,19 +972,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,19 +989,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122973389</v>
+        <v>122970333</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1037,17 +1037,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481565</v>
+        <v>481622</v>
       </c>
       <c r="R5" t="n">
-        <v>6790545</v>
+        <v>6790484</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,19 +1074,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:43</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbilder.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,22 +1096,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122970092</v>
+        <v>122973389</v>
       </c>
       <c r="B6" t="n">
-        <v>78790</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,25 +1120,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481532</v>
+        <v>481565</v>
       </c>
       <c r="R6" t="n">
-        <v>6790516</v>
+        <v>6790545</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1188,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122969836</v>
+        <v>122969848</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>78767</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,16 +1236,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1261,17 +1256,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481538</v>
+        <v>481544</v>
       </c>
       <c r="R7" t="n">
-        <v>6790506</v>
+        <v>6790494</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,19 +1293,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:00</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Torraka i bakgrunden.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,19 +1315,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122970152</v>
+        <v>122970156</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1373,17 +1363,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481577</v>
+        <v>481546</v>
       </c>
       <c r="R8" t="n">
-        <v>6790481</v>
+        <v>6790501</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1410,9 +1400,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,19 +1427,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122973297</v>
+        <v>122969601</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1475,14 +1475,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481575</v>
+        <v>481528</v>
       </c>
       <c r="R9" t="n">
-        <v>6790530</v>
+        <v>6790490</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122973309</v>
+        <v>122973371</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481568</v>
+        <v>481551</v>
       </c>
       <c r="R10" t="n">
-        <v>6790545</v>
+        <v>6790539</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122970352</v>
+        <v>122970092</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>78790</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,25 +1665,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481566</v>
+        <v>481532</v>
       </c>
       <c r="R11" t="n">
-        <v>6790511</v>
+        <v>6790516</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122969848</v>
+        <v>122970211</v>
       </c>
       <c r="B13" t="n">
-        <v>78767</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1908,17 +1908,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481544</v>
+        <v>481559</v>
       </c>
       <c r="R13" t="n">
-        <v>6790494</v>
+        <v>6790521</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1945,14 +1945,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Torraka i bakgrunden.</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,22 +1972,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122969800</v>
+        <v>122970352</v>
       </c>
       <c r="B14" t="n">
-        <v>78790</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1991,25 +1996,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2019,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481538</v>
+        <v>481566</v>
       </c>
       <c r="R14" t="n">
-        <v>6790506</v>
+        <v>6790511</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2054,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2064,7 +2069,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,10 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122970166</v>
+        <v>122970062</v>
       </c>
       <c r="B15" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2103,43 +2108,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481546</v>
+        <v>481533</v>
       </c>
       <c r="R15" t="n">
-        <v>6790501</v>
+        <v>6790513</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2208,10 +2208,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122973404</v>
+        <v>122970166</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2220,41 +2220,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481525</v>
+        <v>481546</v>
       </c>
       <c r="R16" t="n">
-        <v>6790521</v>
+        <v>6790501</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2281,9 +2286,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2298,19 +2313,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122970156</v>
+        <v>122970196</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2346,17 +2361,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481546</v>
+        <v>481598</v>
       </c>
       <c r="R17" t="n">
-        <v>6790501</v>
+        <v>6790481</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2383,19 +2398,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2410,19 +2415,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122970333</v>
+        <v>122969836</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2458,17 +2463,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481622</v>
+        <v>481538</v>
       </c>
       <c r="R18" t="n">
-        <v>6790484</v>
+        <v>6790506</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2495,14 +2500,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbilder.</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,19 +2527,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122973371</v>
+        <v>122973309</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2569,10 +2579,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481551</v>
+        <v>481568</v>
       </c>
       <c r="R19" t="n">
-        <v>6790539</v>
+        <v>6790545</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2604,7 +2614,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2614,7 +2624,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2641,7 +2651,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122969601</v>
+        <v>122970152</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -2681,10 +2691,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481528</v>
+        <v>481577</v>
       </c>
       <c r="R20" t="n">
-        <v>6790490</v>
+        <v>6790481</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2743,7 +2753,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122969887</v>
+        <v>122973297</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -2779,17 +2789,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481534</v>
+        <v>481575</v>
       </c>
       <c r="R21" t="n">
-        <v>6790501</v>
+        <v>6790530</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2816,19 +2826,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2843,22 +2843,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122971770</v>
+        <v>122971698</v>
       </c>
       <c r="B22" t="n">
-        <v>78790</v>
+        <v>8441</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2871,37 +2871,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6434</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481677</v>
+        <v>481661</v>
       </c>
       <c r="R22" t="n">
-        <v>6790565</v>
+        <v>6790503</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2928,19 +2928,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2955,22 +2945,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122971852</v>
+        <v>122971431</v>
       </c>
       <c r="B23" t="n">
-        <v>8441</v>
+        <v>78502</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2979,43 +2969,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481678</v>
+        <v>481658</v>
       </c>
       <c r="R23" t="n">
-        <v>6790570</v>
+        <v>6790494</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3047,7 +3032,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3057,7 +3042,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3084,10 +3069,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122972843</v>
+        <v>122972148</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>78767</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3100,16 +3085,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3124,10 +3109,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481748</v>
+        <v>481755</v>
       </c>
       <c r="R24" t="n">
-        <v>6790465</v>
+        <v>6790500</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3160,6 +3145,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3186,10 +3176,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122971431</v>
+        <v>122972089</v>
       </c>
       <c r="B25" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3202,21 +3192,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3226,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481658</v>
+        <v>481695</v>
       </c>
       <c r="R25" t="n">
-        <v>6790494</v>
+        <v>6790593</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3261,7 +3251,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3271,7 +3261,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3405,10 +3395,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122973048</v>
+        <v>122972843</v>
       </c>
       <c r="B27" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3417,25 +3407,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3445,10 +3435,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481694</v>
+        <v>481748</v>
       </c>
       <c r="R27" t="n">
-        <v>6790479</v>
+        <v>6790465</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3481,11 +3471,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Mindre märgborre på låga.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3512,10 +3497,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122972089</v>
+        <v>122971770</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>78790</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3524,25 +3509,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3552,10 +3537,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481695</v>
+        <v>481677</v>
       </c>
       <c r="R28" t="n">
-        <v>6790593</v>
+        <v>6790565</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -3587,7 +3572,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3597,7 +3582,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3624,10 +3609,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122972148</v>
+        <v>122973048</v>
       </c>
       <c r="B29" t="n">
-        <v>78767</v>
+        <v>8441</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3636,25 +3621,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>230405</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3664,10 +3649,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481755</v>
+        <v>481694</v>
       </c>
       <c r="R29" t="n">
-        <v>6790500</v>
+        <v>6790479</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3704,7 +3689,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Garnlav med miljöbild.</t>
+          <t>Mindre märgborre på låga.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3731,7 +3716,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122972025</v>
+        <v>122971852</v>
       </c>
       <c r="B30" t="n">
         <v>8441</v>
@@ -3776,10 +3761,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481687</v>
+        <v>481678</v>
       </c>
       <c r="R30" t="n">
-        <v>6790643</v>
+        <v>6790570</v>
       </c>
       <c r="S30" t="n">
         <v>9</v>
@@ -3811,7 +3796,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3821,7 +3806,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3848,7 +3833,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122971698</v>
+        <v>122972025</v>
       </c>
       <c r="B31" t="n">
         <v>8441</v>
@@ -3882,19 +3867,24 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481661</v>
+        <v>481687</v>
       </c>
       <c r="R31" t="n">
-        <v>6790503</v>
+        <v>6790643</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3921,9 +3911,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3938,12 +3938,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 33841-2023 artfynd.xlsx
+++ b/artfynd/A 33841-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122969800</v>
+        <v>122970211</v>
       </c>
       <c r="B2" t="n">
-        <v>78790</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481538</v>
+        <v>481559</v>
       </c>
       <c r="R2" t="n">
-        <v>6790506</v>
+        <v>6790521</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122969887</v>
+        <v>122970196</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -823,17 +823,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481534</v>
+        <v>481598</v>
       </c>
       <c r="R3" t="n">
-        <v>6790501</v>
+        <v>6790481</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,19 +860,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,19 +877,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122973404</v>
+        <v>122969836</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -935,17 +925,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481525</v>
+        <v>481538</v>
       </c>
       <c r="R4" t="n">
-        <v>6790521</v>
+        <v>6790506</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,9 +962,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,19 +989,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122970333</v>
+        <v>122970062</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1037,17 +1037,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481622</v>
+        <v>481533</v>
       </c>
       <c r="R5" t="n">
-        <v>6790484</v>
+        <v>6790513</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,14 +1074,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbilder.</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,19 +1101,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122973389</v>
+        <v>122973371</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1148,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481565</v>
+        <v>481551</v>
       </c>
       <c r="R6" t="n">
-        <v>6790545</v>
+        <v>6790539</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1183,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1327,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122970156</v>
+        <v>122970152</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1363,17 +1368,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481546</v>
+        <v>481577</v>
       </c>
       <c r="R8" t="n">
-        <v>6790501</v>
+        <v>6790481</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1400,19 +1405,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,19 +1422,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122969601</v>
+        <v>122970333</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1479,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481528</v>
+        <v>481622</v>
       </c>
       <c r="R9" t="n">
-        <v>6790490</v>
+        <v>6790484</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,6 +1510,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbilder.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122973371</v>
+        <v>122970156</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481551</v>
+        <v>481546</v>
       </c>
       <c r="R10" t="n">
-        <v>6790539</v>
+        <v>6790501</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,7 +1653,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122970092</v>
+        <v>122969800</v>
       </c>
       <c r="B11" t="n">
         <v>78790</v>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481532</v>
+        <v>481538</v>
       </c>
       <c r="R11" t="n">
-        <v>6790516</v>
+        <v>6790506</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122969981</v>
+        <v>122970092</v>
       </c>
       <c r="B12" t="n">
-        <v>78767</v>
+        <v>78790</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1777,41 +1777,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>230405</v>
+        <v>6434</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481565</v>
+        <v>481532</v>
       </c>
       <c r="R12" t="n">
-        <v>6790484</v>
+        <v>6790516</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1838,14 +1838,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Garnlav runt omkring mig i en radie av 40 meter.</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1860,19 +1865,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122970211</v>
+        <v>122973297</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1908,17 +1913,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481559</v>
+        <v>481575</v>
       </c>
       <c r="R13" t="n">
-        <v>6790521</v>
+        <v>6790530</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1945,19 +1950,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,19 +1967,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122970352</v>
+        <v>122973309</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -2024,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481566</v>
+        <v>481568</v>
       </c>
       <c r="R14" t="n">
-        <v>6790511</v>
+        <v>6790545</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2059,7 +2054,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,7 +2064,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,10 +2091,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122970062</v>
+        <v>122969981</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>78767</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2112,16 +2107,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2132,17 +2127,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481533</v>
+        <v>481565</v>
       </c>
       <c r="R15" t="n">
-        <v>6790513</v>
+        <v>6790484</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2169,19 +2164,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:05</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Garnlav runt omkring mig i en radie av 40 meter.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2196,22 +2186,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122970166</v>
+        <v>122969887</v>
       </c>
       <c r="B16" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2220,40 +2210,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481546</v>
+        <v>481534</v>
       </c>
       <c r="R16" t="n">
         <v>6790501</v>
@@ -2288,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2298,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2325,10 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122970196</v>
+        <v>122970166</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2337,41 +2322,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481598</v>
+        <v>481546</v>
       </c>
       <c r="R17" t="n">
-        <v>6790481</v>
+        <v>6790501</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2398,9 +2388,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2415,19 +2415,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122969836</v>
+        <v>122973404</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2463,17 +2463,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481538</v>
+        <v>481525</v>
       </c>
       <c r="R18" t="n">
-        <v>6790506</v>
+        <v>6790521</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2500,19 +2500,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2527,19 +2517,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122973309</v>
+        <v>122969601</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2575,17 +2565,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481568</v>
+        <v>481528</v>
       </c>
       <c r="R19" t="n">
-        <v>6790545</v>
+        <v>6790490</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2612,19 +2602,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2639,19 +2619,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122970152</v>
+        <v>122970352</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -2687,17 +2667,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481577</v>
+        <v>481566</v>
       </c>
       <c r="R20" t="n">
-        <v>6790481</v>
+        <v>6790511</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2724,9 +2704,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2741,19 +2731,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122973297</v>
+        <v>122973389</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -2789,17 +2779,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481575</v>
+        <v>481565</v>
       </c>
       <c r="R21" t="n">
-        <v>6790530</v>
+        <v>6790545</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2826,9 +2816,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2843,22 +2843,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122971698</v>
+        <v>122972148</v>
       </c>
       <c r="B22" t="n">
-        <v>8441</v>
+        <v>78767</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2867,38 +2867,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>230405</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481661</v>
+        <v>481755</v>
       </c>
       <c r="R22" t="n">
-        <v>6790503</v>
+        <v>6790500</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2931,6 +2931,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2957,10 +2962,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122971431</v>
+        <v>122971852</v>
       </c>
       <c r="B23" t="n">
-        <v>78502</v>
+        <v>8441</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2969,38 +2974,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481658</v>
+        <v>481678</v>
       </c>
       <c r="R23" t="n">
-        <v>6790494</v>
+        <v>6790570</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3032,7 +3042,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3042,7 +3052,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3069,10 +3079,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122972148</v>
+        <v>122970459</v>
       </c>
       <c r="B24" t="n">
-        <v>78767</v>
+        <v>57494</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3085,34 +3095,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>230405</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481755</v>
+        <v>481658</v>
       </c>
       <c r="R24" t="n">
-        <v>6790500</v>
+        <v>6790493</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3149,7 +3159,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Garnlav med miljöbild.</t>
+          <t>Miljöbilder och spillkråka.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3288,10 +3298,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122970459</v>
+        <v>122971770</v>
       </c>
       <c r="B26" t="n">
-        <v>57494</v>
+        <v>78790</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3300,41 +3310,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481658</v>
+        <v>481677</v>
       </c>
       <c r="R26" t="n">
-        <v>6790493</v>
+        <v>6790565</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3361,14 +3371,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Miljöbilder och spillkråka.</t>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3383,22 +3398,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122972843</v>
+        <v>122971431</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3411,37 +3426,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481748</v>
+        <v>481658</v>
       </c>
       <c r="R27" t="n">
-        <v>6790465</v>
+        <v>6790494</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3468,9 +3483,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3485,22 +3510,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122971770</v>
+        <v>122971698</v>
       </c>
       <c r="B28" t="n">
-        <v>78790</v>
+        <v>8441</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3513,37 +3538,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6434</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481677</v>
+        <v>481661</v>
       </c>
       <c r="R28" t="n">
-        <v>6790565</v>
+        <v>6790503</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3570,19 +3595,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3597,22 +3612,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122973048</v>
+        <v>122972843</v>
       </c>
       <c r="B29" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3621,25 +3636,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3649,10 +3664,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481694</v>
+        <v>481748</v>
       </c>
       <c r="R29" t="n">
-        <v>6790479</v>
+        <v>6790465</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3685,11 +3700,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Mindre märgborre på låga.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3716,7 +3726,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122971852</v>
+        <v>122973048</v>
       </c>
       <c r="B30" t="n">
         <v>8441</v>
@@ -3750,24 +3760,19 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481678</v>
+        <v>481694</v>
       </c>
       <c r="R30" t="n">
-        <v>6790570</v>
+        <v>6790479</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3794,19 +3799,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:56</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Mindre märgborre på låga.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3821,12 +3821,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 33841-2023 artfynd.xlsx
+++ b/artfynd/A 33841-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122970211</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122970196</v>
+        <v>122970062</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,17 +823,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481598</v>
+        <v>481533</v>
       </c>
       <c r="R3" t="n">
-        <v>6790481</v>
+        <v>6790513</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,9 +860,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122969836</v>
+        <v>122969887</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481538</v>
+        <v>481534</v>
       </c>
       <c r="R4" t="n">
-        <v>6790506</v>
+        <v>6790501</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -964,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122970062</v>
+        <v>122969848</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>78770</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,16 +1027,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1037,17 +1047,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481533</v>
+        <v>481544</v>
       </c>
       <c r="R5" t="n">
-        <v>6790513</v>
+        <v>6790494</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,19 +1084,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:05</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Torraka i bakgrunden.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,22 +1106,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122973371</v>
+        <v>122969601</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,17 +1154,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481551</v>
+        <v>481528</v>
       </c>
       <c r="R6" t="n">
-        <v>6790539</v>
+        <v>6790490</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1186,19 +1191,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,22 +1208,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122969848</v>
+        <v>122973389</v>
       </c>
       <c r="B7" t="n">
-        <v>78767</v>
+        <v>78769</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,16 +1236,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1261,17 +1256,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481544</v>
+        <v>481565</v>
       </c>
       <c r="R7" t="n">
-        <v>6790494</v>
+        <v>6790545</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,14 +1293,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Torraka i bakgrunden.</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,22 +1320,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122970152</v>
+        <v>122970333</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481577</v>
+        <v>481622</v>
       </c>
       <c r="R8" t="n">
-        <v>6790481</v>
+        <v>6790484</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,6 +1408,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbilder.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122970333</v>
+        <v>122969981</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>78770</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,16 +1455,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1474,7 +1479,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481622</v>
+        <v>481565</v>
       </c>
       <c r="R9" t="n">
         <v>6790484</v>
@@ -1514,7 +1519,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Garnlav med miljöbilder.</t>
+          <t>Garnlav runt omkring mig i en radie av 40 meter.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122970156</v>
+        <v>122973309</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1581,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481546</v>
+        <v>481568</v>
       </c>
       <c r="R10" t="n">
-        <v>6790501</v>
+        <v>6790545</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1616,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1631,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122969800</v>
+        <v>122973297</v>
       </c>
       <c r="B11" t="n">
-        <v>78790</v>
+        <v>78769</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,41 +1670,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481538</v>
+        <v>481575</v>
       </c>
       <c r="R11" t="n">
-        <v>6790506</v>
+        <v>6790530</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1726,19 +1731,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,22 +1748,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122970092</v>
+        <v>122970166</v>
       </c>
       <c r="B12" t="n">
-        <v>78790</v>
+        <v>8441</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,34 +1776,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6434</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481532</v>
+        <v>481546</v>
       </c>
       <c r="R12" t="n">
-        <v>6790516</v>
+        <v>6790501</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122973297</v>
+        <v>122969800</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>78793</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1889,41 +1889,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481575</v>
+        <v>481538</v>
       </c>
       <c r="R13" t="n">
-        <v>6790530</v>
+        <v>6790506</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1950,9 +1950,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,22 +1977,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122973309</v>
+        <v>122970152</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2015,17 +2025,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481568</v>
+        <v>481577</v>
       </c>
       <c r="R14" t="n">
-        <v>6790545</v>
+        <v>6790481</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2052,19 +2062,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,22 +2079,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122969981</v>
+        <v>122969836</v>
       </c>
       <c r="B15" t="n">
-        <v>78767</v>
+        <v>78769</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2107,16 +2107,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2127,17 +2127,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481565</v>
+        <v>481538</v>
       </c>
       <c r="R15" t="n">
-        <v>6790484</v>
+        <v>6790506</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2164,14 +2164,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Garnlav runt omkring mig i en radie av 40 meter.</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2186,22 +2191,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122969887</v>
+        <v>122970156</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2238,7 +2243,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481534</v>
+        <v>481546</v>
       </c>
       <c r="R16" t="n">
         <v>6790501</v>
@@ -2273,7 +2278,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2288,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,10 +2315,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122970166</v>
+        <v>122973371</v>
       </c>
       <c r="B17" t="n">
-        <v>8441</v>
+        <v>78769</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2322,43 +2327,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481546</v>
+        <v>481551</v>
       </c>
       <c r="R17" t="n">
-        <v>6790501</v>
+        <v>6790539</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2427,10 +2427,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122973404</v>
+        <v>122970092</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>78793</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2439,41 +2439,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481525</v>
+        <v>481532</v>
       </c>
       <c r="R18" t="n">
-        <v>6790521</v>
+        <v>6790516</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2500,9 +2500,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,22 +2527,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122969601</v>
+        <v>122970196</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2569,10 +2579,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481528</v>
+        <v>481598</v>
       </c>
       <c r="R19" t="n">
-        <v>6790490</v>
+        <v>6790481</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2634,7 +2644,7 @@
         <v>122970352</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2743,10 +2753,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122973389</v>
+        <v>122973404</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2779,17 +2789,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481565</v>
+        <v>481525</v>
       </c>
       <c r="R21" t="n">
-        <v>6790545</v>
+        <v>6790521</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2816,19 +2826,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2843,12 +2843,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2858,7 +2858,7 @@
         <v>122972148</v>
       </c>
       <c r="B22" t="n">
-        <v>78767</v>
+        <v>78770</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122971852</v>
+        <v>122971431</v>
       </c>
       <c r="B23" t="n">
-        <v>8441</v>
+        <v>78505</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2974,43 +2974,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481678</v>
+        <v>481658</v>
       </c>
       <c r="R23" t="n">
-        <v>6790570</v>
+        <v>6790494</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3042,7 +3037,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3052,7 +3047,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3079,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122970459</v>
+        <v>122972843</v>
       </c>
       <c r="B24" t="n">
-        <v>57494</v>
+        <v>78769</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3095,34 +3090,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481658</v>
+        <v>481748</v>
       </c>
       <c r="R24" t="n">
-        <v>6790493</v>
+        <v>6790465</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3155,11 +3150,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Miljöbilder och spillkråka.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3186,10 +3176,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122972089</v>
+        <v>122971852</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3198,38 +3188,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481695</v>
+        <v>481678</v>
       </c>
       <c r="R25" t="n">
-        <v>6790593</v>
+        <v>6790570</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3261,7 +3256,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3271,7 +3266,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3298,10 +3293,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122971770</v>
+        <v>122971698</v>
       </c>
       <c r="B26" t="n">
-        <v>78790</v>
+        <v>8441</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3314,37 +3309,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6434</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481677</v>
+        <v>481661</v>
       </c>
       <c r="R26" t="n">
-        <v>6790565</v>
+        <v>6790503</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3371,19 +3366,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3398,22 +3383,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122971431</v>
+        <v>122971770</v>
       </c>
       <c r="B27" t="n">
-        <v>78502</v>
+        <v>78793</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3422,25 +3407,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3450,10 +3435,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481658</v>
+        <v>481677</v>
       </c>
       <c r="R27" t="n">
-        <v>6790494</v>
+        <v>6790565</v>
       </c>
       <c r="S27" t="n">
         <v>9</v>
@@ -3485,7 +3470,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3495,7 +3480,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3522,10 +3507,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122971698</v>
+        <v>122970459</v>
       </c>
       <c r="B28" t="n">
-        <v>8441</v>
+        <v>57497</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3534,25 +3519,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3562,10 +3547,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481661</v>
+        <v>481658</v>
       </c>
       <c r="R28" t="n">
-        <v>6790503</v>
+        <v>6790493</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3598,6 +3583,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Miljöbilder och spillkråka.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3624,10 +3614,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122972843</v>
+        <v>122973048</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3636,25 +3626,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3664,10 +3654,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481748</v>
+        <v>481694</v>
       </c>
       <c r="R29" t="n">
-        <v>6790465</v>
+        <v>6790479</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3700,6 +3690,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Mindre märgborre på låga.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3726,10 +3721,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122973048</v>
+        <v>122972089</v>
       </c>
       <c r="B30" t="n">
-        <v>8441</v>
+        <v>78769</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3738,41 +3733,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481694</v>
+        <v>481695</v>
       </c>
       <c r="R30" t="n">
-        <v>6790479</v>
+        <v>6790593</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3799,14 +3794,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Mindre märgborre på låga.</t>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3821,12 +3821,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 33841-2023 artfynd.xlsx
+++ b/artfynd/A 33841-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122970211</v>
+        <v>122969887</v>
       </c>
       <c r="B2" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481559</v>
+        <v>481534</v>
       </c>
       <c r="R2" t="n">
-        <v>6790521</v>
+        <v>6790501</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122970062</v>
+        <v>122970166</v>
       </c>
       <c r="B3" t="n">
-        <v>78769</v>
+        <v>8441</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481533</v>
+        <v>481546</v>
       </c>
       <c r="R3" t="n">
-        <v>6790513</v>
+        <v>6790501</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122969887</v>
+        <v>122973371</v>
       </c>
       <c r="B4" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481534</v>
+        <v>481551</v>
       </c>
       <c r="R4" t="n">
-        <v>6790501</v>
+        <v>6790539</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122969848</v>
+        <v>122970352</v>
       </c>
       <c r="B5" t="n">
-        <v>78770</v>
+        <v>78771</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,16 +1032,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1047,17 +1052,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481544</v>
+        <v>481566</v>
       </c>
       <c r="R5" t="n">
-        <v>6790494</v>
+        <v>6790511</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,14 +1089,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Torraka i bakgrunden.</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,22 +1116,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122969601</v>
+        <v>122969836</v>
       </c>
       <c r="B6" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,17 +1164,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481528</v>
+        <v>481538</v>
       </c>
       <c r="R6" t="n">
-        <v>6790490</v>
+        <v>6790506</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,9 +1201,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,22 +1228,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122973389</v>
+        <v>122970211</v>
       </c>
       <c r="B7" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481565</v>
+        <v>481559</v>
       </c>
       <c r="R7" t="n">
-        <v>6790545</v>
+        <v>6790521</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1295,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122970333</v>
+        <v>122969981</v>
       </c>
       <c r="B8" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,16 +1368,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1372,7 +1392,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481622</v>
+        <v>481565</v>
       </c>
       <c r="R8" t="n">
         <v>6790484</v>
@@ -1412,7 +1432,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Garnlav med miljöbilder.</t>
+          <t>Garnlav runt omkring mig i en radie av 40 meter.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122969981</v>
+        <v>122973297</v>
       </c>
       <c r="B9" t="n">
-        <v>78770</v>
+        <v>78771</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1455,16 +1475,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1475,14 +1495,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481565</v>
+        <v>481575</v>
       </c>
       <c r="R9" t="n">
-        <v>6790484</v>
+        <v>6790530</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,11 +1535,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Garnlav runt omkring mig i en radie av 40 meter.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,7 +1564,7 @@
         <v>122973309</v>
       </c>
       <c r="B10" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1658,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122973297</v>
+        <v>122970333</v>
       </c>
       <c r="B11" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1694,14 +1709,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481575</v>
+        <v>481622</v>
       </c>
       <c r="R11" t="n">
-        <v>6790530</v>
+        <v>6790484</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,6 +1749,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbilder.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,10 +1780,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122970166</v>
+        <v>122970092</v>
       </c>
       <c r="B12" t="n">
-        <v>8441</v>
+        <v>78795</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1776,39 +1796,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6434</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481546</v>
+        <v>481532</v>
       </c>
       <c r="R12" t="n">
-        <v>6790501</v>
+        <v>6790516</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1840,7 +1855,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1850,7 +1865,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,7 +1895,7 @@
         <v>122969800</v>
       </c>
       <c r="B13" t="n">
-        <v>78793</v>
+        <v>78795</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1992,7 +2007,7 @@
         <v>122970152</v>
       </c>
       <c r="B14" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2091,10 +2106,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122969836</v>
+        <v>122973404</v>
       </c>
       <c r="B15" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2127,17 +2142,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481538</v>
+        <v>481525</v>
       </c>
       <c r="R15" t="n">
-        <v>6790506</v>
+        <v>6790521</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2164,19 +2179,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,22 +2196,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122970156</v>
+        <v>122970062</v>
       </c>
       <c r="B16" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2243,10 +2248,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481546</v>
+        <v>481533</v>
       </c>
       <c r="R16" t="n">
-        <v>6790501</v>
+        <v>6790513</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2278,7 +2283,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2288,7 +2293,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2315,10 +2320,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122973371</v>
+        <v>122970156</v>
       </c>
       <c r="B17" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2355,10 +2360,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481551</v>
+        <v>481546</v>
       </c>
       <c r="R17" t="n">
-        <v>6790539</v>
+        <v>6790501</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2390,7 +2395,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2400,7 +2405,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2427,10 +2432,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122970092</v>
+        <v>122969601</v>
       </c>
       <c r="B18" t="n">
-        <v>78793</v>
+        <v>78771</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2439,41 +2444,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481532</v>
+        <v>481528</v>
       </c>
       <c r="R18" t="n">
-        <v>6790516</v>
+        <v>6790490</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2500,19 +2505,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2527,22 +2522,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122970196</v>
+        <v>122973389</v>
       </c>
       <c r="B19" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2575,17 +2570,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481598</v>
+        <v>481565</v>
       </c>
       <c r="R19" t="n">
-        <v>6790481</v>
+        <v>6790545</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2612,9 +2607,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2629,22 +2634,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122970352</v>
+        <v>122970196</v>
       </c>
       <c r="B20" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2677,17 +2682,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481566</v>
+        <v>481598</v>
       </c>
       <c r="R20" t="n">
-        <v>6790511</v>
+        <v>6790481</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2714,19 +2719,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2741,22 +2736,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122973404</v>
+        <v>122969848</v>
       </c>
       <c r="B21" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2769,16 +2764,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2789,14 +2784,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481525</v>
+        <v>481544</v>
       </c>
       <c r="R21" t="n">
-        <v>6790521</v>
+        <v>6790494</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2829,6 +2824,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Torraka i bakgrunden.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,10 +2855,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122972148</v>
+        <v>122971852</v>
       </c>
       <c r="B22" t="n">
-        <v>78770</v>
+        <v>8441</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2867,41 +2867,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>230405</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481755</v>
+        <v>481678</v>
       </c>
       <c r="R22" t="n">
-        <v>6790500</v>
+        <v>6790570</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2928,14 +2933,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbild.</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2950,12 +2960,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2965,7 +2975,7 @@
         <v>122971431</v>
       </c>
       <c r="B23" t="n">
-        <v>78505</v>
+        <v>78507</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3074,10 +3084,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122972843</v>
+        <v>122970459</v>
       </c>
       <c r="B24" t="n">
-        <v>78769</v>
+        <v>57497</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3090,34 +3100,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481748</v>
+        <v>481658</v>
       </c>
       <c r="R24" t="n">
-        <v>6790465</v>
+        <v>6790493</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3150,6 +3160,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Miljöbilder och spillkråka.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3176,10 +3191,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122971852</v>
+        <v>122972089</v>
       </c>
       <c r="B25" t="n">
-        <v>8441</v>
+        <v>78771</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3188,43 +3203,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481678</v>
+        <v>481695</v>
       </c>
       <c r="R25" t="n">
-        <v>6790570</v>
+        <v>6790593</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3256,7 +3266,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3266,7 +3276,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3293,7 +3303,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122971698</v>
+        <v>122973048</v>
       </c>
       <c r="B26" t="n">
         <v>8441</v>
@@ -3329,14 +3339,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481661</v>
+        <v>481694</v>
       </c>
       <c r="R26" t="n">
-        <v>6790503</v>
+        <v>6790479</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3369,6 +3379,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Mindre märgborre på låga.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3395,10 +3410,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122971770</v>
+        <v>122972148</v>
       </c>
       <c r="B27" t="n">
-        <v>78793</v>
+        <v>78772</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3407,41 +3422,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6434</v>
+        <v>230405</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481677</v>
+        <v>481755</v>
       </c>
       <c r="R27" t="n">
-        <v>6790565</v>
+        <v>6790500</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3468,19 +3483,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:53</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3495,22 +3505,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122970459</v>
+        <v>122971698</v>
       </c>
       <c r="B28" t="n">
-        <v>57497</v>
+        <v>8441</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3519,25 +3529,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3547,10 +3557,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481658</v>
+        <v>481661</v>
       </c>
       <c r="R28" t="n">
-        <v>6790493</v>
+        <v>6790503</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3583,11 +3593,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Miljöbilder och spillkråka.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3614,10 +3619,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122973048</v>
+        <v>122971770</v>
       </c>
       <c r="B29" t="n">
-        <v>8441</v>
+        <v>78795</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3630,37 +3635,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6434</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481694</v>
+        <v>481677</v>
       </c>
       <c r="R29" t="n">
-        <v>6790479</v>
+        <v>6790565</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3687,14 +3692,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Mindre märgborre på låga.</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3709,22 +3719,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122972089</v>
+        <v>122972843</v>
       </c>
       <c r="B30" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3757,17 +3767,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481695</v>
+        <v>481748</v>
       </c>
       <c r="R30" t="n">
-        <v>6790593</v>
+        <v>6790465</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3794,19 +3804,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3821,12 +3821,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 33841-2023 artfynd.xlsx
+++ b/artfynd/A 33841-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122970166</v>
+        <v>122973371</v>
       </c>
       <c r="B3" t="n">
-        <v>8441</v>
+        <v>78771</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481546</v>
+        <v>481551</v>
       </c>
       <c r="R3" t="n">
-        <v>6790501</v>
+        <v>6790539</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122973371</v>
+        <v>122970352</v>
       </c>
       <c r="B4" t="n">
         <v>78771</v>
@@ -944,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481551</v>
+        <v>481566</v>
       </c>
       <c r="R4" t="n">
-        <v>6790539</v>
+        <v>6790511</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122970352</v>
+        <v>122970166</v>
       </c>
       <c r="B5" t="n">
-        <v>78771</v>
+        <v>8441</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,38 +1023,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481566</v>
+        <v>481546</v>
       </c>
       <c r="R5" t="n">
-        <v>6790511</v>
+        <v>6790501</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122973309</v>
+        <v>122970092</v>
       </c>
       <c r="B10" t="n">
-        <v>78771</v>
+        <v>78795</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,25 +1573,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481568</v>
+        <v>481532</v>
       </c>
       <c r="R10" t="n">
-        <v>6790545</v>
+        <v>6790516</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,7 +1673,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122970333</v>
+        <v>122973309</v>
       </c>
       <c r="B11" t="n">
         <v>78771</v>
@@ -1709,17 +1709,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481622</v>
+        <v>481568</v>
       </c>
       <c r="R11" t="n">
-        <v>6790484</v>
+        <v>6790545</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1746,14 +1746,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbilder.</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,22 +1773,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122970092</v>
+        <v>122970333</v>
       </c>
       <c r="B12" t="n">
-        <v>78795</v>
+        <v>78771</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1792,41 +1797,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481532</v>
+        <v>481622</v>
       </c>
       <c r="R12" t="n">
-        <v>6790516</v>
+        <v>6790484</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1853,19 +1858,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:05</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbilder.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,12 +1880,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 33841-2023 artfynd.xlsx
+++ b/artfynd/A 33841-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122969887</v>
+        <v>122970211</v>
       </c>
       <c r="B2" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481534</v>
+        <v>481559</v>
       </c>
       <c r="R2" t="n">
-        <v>6790501</v>
+        <v>6790521</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122973371</v>
+        <v>122970062</v>
       </c>
       <c r="B3" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481551</v>
+        <v>481533</v>
       </c>
       <c r="R3" t="n">
-        <v>6790539</v>
+        <v>6790513</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122970352</v>
+        <v>122973371</v>
       </c>
       <c r="B4" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481566</v>
+        <v>481551</v>
       </c>
       <c r="R4" t="n">
-        <v>6790511</v>
+        <v>6790539</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122970166</v>
+        <v>122970352</v>
       </c>
       <c r="B5" t="n">
-        <v>8441</v>
+        <v>78772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,43 +1023,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481546</v>
+        <v>481566</v>
       </c>
       <c r="R5" t="n">
-        <v>6790501</v>
+        <v>6790511</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122969836</v>
+        <v>122970166</v>
       </c>
       <c r="B6" t="n">
-        <v>78771</v>
+        <v>8441</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,38 +1135,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481538</v>
+        <v>481546</v>
       </c>
       <c r="R6" t="n">
-        <v>6790506</v>
+        <v>6790501</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122970211</v>
+        <v>122970196</v>
       </c>
       <c r="B7" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,17 +1276,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481559</v>
+        <v>481598</v>
       </c>
       <c r="R7" t="n">
-        <v>6790521</v>
+        <v>6790481</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1313,19 +1313,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,19 +1330,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122969981</v>
+        <v>122970156</v>
       </c>
       <c r="B8" t="n">
         <v>78772</v>
@@ -1368,16 +1358,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1388,17 +1378,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481565</v>
+        <v>481546</v>
       </c>
       <c r="R8" t="n">
-        <v>6790484</v>
+        <v>6790501</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1425,14 +1415,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Garnlav runt omkring mig i en radie av 40 meter.</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,22 +1442,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122973297</v>
+        <v>122973404</v>
       </c>
       <c r="B9" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481575</v>
+        <v>481525</v>
       </c>
       <c r="R9" t="n">
-        <v>6790530</v>
+        <v>6790521</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122970092</v>
+        <v>122973309</v>
       </c>
       <c r="B10" t="n">
-        <v>78795</v>
+        <v>78772</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,25 +1568,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481532</v>
+        <v>481568</v>
       </c>
       <c r="R10" t="n">
-        <v>6790516</v>
+        <v>6790545</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1636,7 +1631,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1646,7 +1641,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122973309</v>
+        <v>122969800</v>
       </c>
       <c r="B11" t="n">
-        <v>78771</v>
+        <v>78796</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1685,25 +1680,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1713,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481568</v>
+        <v>481538</v>
       </c>
       <c r="R11" t="n">
-        <v>6790545</v>
+        <v>6790506</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1748,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1758,7 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,10 +1780,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122970333</v>
+        <v>122969836</v>
       </c>
       <c r="B12" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,17 +1816,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481622</v>
+        <v>481538</v>
       </c>
       <c r="R12" t="n">
-        <v>6790484</v>
+        <v>6790506</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1858,14 +1853,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbilder.</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,22 +1880,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122969800</v>
+        <v>122969848</v>
       </c>
       <c r="B13" t="n">
-        <v>78795</v>
+        <v>78773</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1904,41 +1904,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6434</v>
+        <v>230405</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481538</v>
+        <v>481544</v>
       </c>
       <c r="R13" t="n">
-        <v>6790506</v>
+        <v>6790494</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1965,19 +1965,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:00</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Torraka i bakgrunden.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1992,22 +1987,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122970152</v>
+        <v>122969601</v>
       </c>
       <c r="B14" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,10 +2039,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481577</v>
+        <v>481528</v>
       </c>
       <c r="R14" t="n">
-        <v>6790481</v>
+        <v>6790490</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2106,10 +2101,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122973404</v>
+        <v>122970333</v>
       </c>
       <c r="B15" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2142,14 +2137,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481525</v>
+        <v>481622</v>
       </c>
       <c r="R15" t="n">
-        <v>6790521</v>
+        <v>6790484</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2182,6 +2177,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbilder.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2208,10 +2208,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122970062</v>
+        <v>122970092</v>
       </c>
       <c r="B16" t="n">
-        <v>78771</v>
+        <v>78796</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2220,25 +2220,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2248,10 +2248,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481533</v>
+        <v>481532</v>
       </c>
       <c r="R16" t="n">
-        <v>6790513</v>
+        <v>6790516</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2320,10 +2320,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122970156</v>
+        <v>122970152</v>
       </c>
       <c r="B17" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2356,17 +2356,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481546</v>
+        <v>481577</v>
       </c>
       <c r="R17" t="n">
-        <v>6790501</v>
+        <v>6790481</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2393,19 +2393,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2420,22 +2410,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122969601</v>
+        <v>122973297</v>
       </c>
       <c r="B18" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2468,14 +2458,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481528</v>
+        <v>481575</v>
       </c>
       <c r="R18" t="n">
-        <v>6790490</v>
+        <v>6790530</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2537,7 +2527,7 @@
         <v>122973389</v>
       </c>
       <c r="B19" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2646,10 +2636,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122970196</v>
+        <v>122969887</v>
       </c>
       <c r="B20" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2682,17 +2672,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481598</v>
+        <v>481534</v>
       </c>
       <c r="R20" t="n">
-        <v>6790481</v>
+        <v>6790501</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2719,9 +2709,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2736,22 +2736,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122969848</v>
+        <v>122969981</v>
       </c>
       <c r="B21" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481544</v>
+        <v>481565</v>
       </c>
       <c r="R21" t="n">
-        <v>6790494</v>
+        <v>6790484</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Torraka i bakgrunden.</t>
+          <t>Garnlav runt omkring mig i en radie av 40 meter.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,10 +2855,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122971852</v>
+        <v>122972843</v>
       </c>
       <c r="B22" t="n">
-        <v>8441</v>
+        <v>78772</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2867,46 +2867,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481678</v>
+        <v>481748</v>
       </c>
       <c r="R22" t="n">
-        <v>6790570</v>
+        <v>6790465</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2933,19 +2928,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2960,22 +2945,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122971431</v>
+        <v>122973048</v>
       </c>
       <c r="B23" t="n">
-        <v>78507</v>
+        <v>8441</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2984,41 +2969,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481658</v>
+        <v>481694</v>
       </c>
       <c r="R23" t="n">
-        <v>6790494</v>
+        <v>6790479</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3045,19 +3030,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:44</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Mindre märgborre på låga.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3072,22 +3052,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122970459</v>
+        <v>122972025</v>
       </c>
       <c r="B24" t="n">
-        <v>57497</v>
+        <v>8441</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3096,41 +3076,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481658</v>
+        <v>481687</v>
       </c>
       <c r="R24" t="n">
-        <v>6790493</v>
+        <v>6790643</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3157,14 +3142,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Miljöbilder och spillkråka.</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3179,22 +3169,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122972089</v>
+        <v>122970459</v>
       </c>
       <c r="B25" t="n">
-        <v>78771</v>
+        <v>57497</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3207,37 +3197,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481695</v>
+        <v>481658</v>
       </c>
       <c r="R25" t="n">
-        <v>6790593</v>
+        <v>6790493</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3264,19 +3254,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:02</t>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Miljöbilder och spillkråka.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3291,22 +3276,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122973048</v>
+        <v>122972148</v>
       </c>
       <c r="B26" t="n">
-        <v>8441</v>
+        <v>78773</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3315,25 +3300,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>230405</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3343,10 +3328,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481694</v>
+        <v>481755</v>
       </c>
       <c r="R26" t="n">
-        <v>6790479</v>
+        <v>6790500</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3383,7 +3368,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Mindre märgborre på låga.</t>
+          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3410,10 +3395,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122972148</v>
+        <v>122971698</v>
       </c>
       <c r="B27" t="n">
-        <v>78772</v>
+        <v>8441</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3422,38 +3407,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>230405</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481755</v>
+        <v>481661</v>
       </c>
       <c r="R27" t="n">
-        <v>6790500</v>
+        <v>6790503</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3486,11 +3471,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3517,10 +3497,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122971698</v>
+        <v>122971431</v>
       </c>
       <c r="B28" t="n">
-        <v>8441</v>
+        <v>78508</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3529,41 +3509,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481661</v>
+        <v>481658</v>
       </c>
       <c r="R28" t="n">
-        <v>6790503</v>
+        <v>6790494</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3590,9 +3570,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3607,22 +3597,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122971770</v>
+        <v>122971852</v>
       </c>
       <c r="B29" t="n">
-        <v>78795</v>
+        <v>8441</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3635,34 +3625,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6434</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481677</v>
+        <v>481678</v>
       </c>
       <c r="R29" t="n">
-        <v>6790565</v>
+        <v>6790570</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
@@ -3694,7 +3689,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3704,7 +3699,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3731,10 +3726,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122972843</v>
+        <v>122972089</v>
       </c>
       <c r="B30" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3767,17 +3762,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481748</v>
+        <v>481695</v>
       </c>
       <c r="R30" t="n">
-        <v>6790465</v>
+        <v>6790593</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3804,9 +3799,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3821,22 +3826,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122972025</v>
+        <v>122971770</v>
       </c>
       <c r="B31" t="n">
-        <v>8441</v>
+        <v>78796</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3849,39 +3854,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6434</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481687</v>
+        <v>481677</v>
       </c>
       <c r="R31" t="n">
-        <v>6790643</v>
+        <v>6790565</v>
       </c>
       <c r="S31" t="n">
         <v>9</v>
@@ -3913,7 +3913,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 33841-2023 artfynd.xlsx
+++ b/artfynd/A 33841-2023 artfynd.xlsx
@@ -3517,10 +3517,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122972148</v>
+        <v>122970459</v>
       </c>
       <c r="B28" t="n">
-        <v>78776</v>
+        <v>57497</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3533,34 +3533,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>230405</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481755</v>
+        <v>481658</v>
       </c>
       <c r="R28" t="n">
-        <v>6790500</v>
+        <v>6790493</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3597,7 +3597,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Garnlav med miljöbild.</t>
+          <t>Miljöbilder och spillkråka.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3624,10 +3624,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122970459</v>
+        <v>122972148</v>
       </c>
       <c r="B29" t="n">
-        <v>57497</v>
+        <v>78776</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3640,34 +3640,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>230405</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481658</v>
+        <v>481755</v>
       </c>
       <c r="R29" t="n">
-        <v>6790493</v>
+        <v>6790500</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Miljöbilder och spillkråka.</t>
+          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 33841-2023 artfynd.xlsx
+++ b/artfynd/A 33841-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122970166</v>
+        <v>122973404</v>
       </c>
       <c r="B2" t="n">
-        <v>8441</v>
+        <v>78781</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481546</v>
+        <v>481525</v>
       </c>
       <c r="R2" t="n">
-        <v>6790501</v>
+        <v>6790521</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,19 +748,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122970352</v>
+        <v>122973297</v>
       </c>
       <c r="B3" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481566</v>
+        <v>481575</v>
       </c>
       <c r="R3" t="n">
-        <v>6790511</v>
+        <v>6790530</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,19 +850,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122973297</v>
+        <v>122969601</v>
       </c>
       <c r="B4" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,14 +915,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481575</v>
+        <v>481528</v>
       </c>
       <c r="R4" t="n">
-        <v>6790530</v>
+        <v>6790490</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122970196</v>
+        <v>122970062</v>
       </c>
       <c r="B5" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,17 +1017,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481598</v>
+        <v>481533</v>
       </c>
       <c r="R5" t="n">
-        <v>6790481</v>
+        <v>6790513</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,9 +1054,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,22 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122973371</v>
+        <v>122970166</v>
       </c>
       <c r="B6" t="n">
-        <v>78775</v>
+        <v>8445</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,38 +1105,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481551</v>
+        <v>481546</v>
       </c>
       <c r="R6" t="n">
-        <v>6790539</v>
+        <v>6790501</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1183,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122970156</v>
+        <v>122970333</v>
       </c>
       <c r="B7" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,17 +1246,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481546</v>
+        <v>481622</v>
       </c>
       <c r="R7" t="n">
-        <v>6790501</v>
+        <v>6790484</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,19 +1283,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:08</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbilder.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,22 +1305,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122970333</v>
+        <v>122973389</v>
       </c>
       <c r="B8" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,17 +1353,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481622</v>
+        <v>481565</v>
       </c>
       <c r="R8" t="n">
-        <v>6790484</v>
+        <v>6790545</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1405,14 +1390,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbilder.</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,22 +1417,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122973389</v>
+        <v>122973371</v>
       </c>
       <c r="B9" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481565</v>
+        <v>481551</v>
       </c>
       <c r="R9" t="n">
-        <v>6790545</v>
+        <v>6790539</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1514,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1524,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1554,7 +1544,7 @@
         <v>122969848</v>
       </c>
       <c r="B10" t="n">
-        <v>78776</v>
+        <v>78782</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1658,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122973309</v>
+        <v>122970211</v>
       </c>
       <c r="B11" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481568</v>
+        <v>481559</v>
       </c>
       <c r="R11" t="n">
-        <v>6790545</v>
+        <v>6790521</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1733,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1743,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122970092</v>
+        <v>122969887</v>
       </c>
       <c r="B12" t="n">
-        <v>78799</v>
+        <v>78781</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,25 +1772,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1810,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481532</v>
+        <v>481534</v>
       </c>
       <c r="R12" t="n">
-        <v>6790516</v>
+        <v>6790501</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1845,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1855,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122969800</v>
+        <v>122970352</v>
       </c>
       <c r="B13" t="n">
-        <v>78799</v>
+        <v>78781</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1894,25 +1884,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1922,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481538</v>
+        <v>481566</v>
       </c>
       <c r="R13" t="n">
-        <v>6790506</v>
+        <v>6790511</v>
       </c>
       <c r="S13" t="n">
         <v>9</v>
@@ -1957,7 +1947,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1967,7 +1957,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1994,10 +1984,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122969981</v>
+        <v>122973309</v>
       </c>
       <c r="B14" t="n">
-        <v>78776</v>
+        <v>78781</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2010,16 +2000,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2030,17 +2020,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481565</v>
+        <v>481568</v>
       </c>
       <c r="R14" t="n">
-        <v>6790484</v>
+        <v>6790545</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2067,14 +2057,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Garnlav runt omkring mig i en radie av 40 meter.</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,22 +2084,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122969887</v>
+        <v>122970196</v>
       </c>
       <c r="B15" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2137,17 +2132,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481534</v>
+        <v>481598</v>
       </c>
       <c r="R15" t="n">
-        <v>6790501</v>
+        <v>6790481</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2174,19 +2169,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2201,22 +2186,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122969836</v>
+        <v>122970156</v>
       </c>
       <c r="B16" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2253,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481538</v>
+        <v>481546</v>
       </c>
       <c r="R16" t="n">
-        <v>6790506</v>
+        <v>6790501</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2288,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2298,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2328,7 +2313,7 @@
         <v>122970152</v>
       </c>
       <c r="B17" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2427,10 +2412,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122970211</v>
+        <v>122970092</v>
       </c>
       <c r="B18" t="n">
-        <v>78775</v>
+        <v>78805</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2439,25 +2424,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2467,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481559</v>
+        <v>481532</v>
       </c>
       <c r="R18" t="n">
-        <v>6790521</v>
+        <v>6790516</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2502,7 +2487,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2512,7 +2497,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2539,10 +2524,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122973404</v>
+        <v>122969981</v>
       </c>
       <c r="B19" t="n">
-        <v>78775</v>
+        <v>78782</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2555,16 +2540,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2575,14 +2560,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481525</v>
+        <v>481565</v>
       </c>
       <c r="R19" t="n">
-        <v>6790521</v>
+        <v>6790484</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,6 +2600,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Garnlav runt omkring mig i en radie av 40 meter.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2641,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122970062</v>
+        <v>122969800</v>
       </c>
       <c r="B20" t="n">
-        <v>78775</v>
+        <v>78805</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2653,25 +2643,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2681,10 +2671,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481533</v>
+        <v>481538</v>
       </c>
       <c r="R20" t="n">
-        <v>6790513</v>
+        <v>6790506</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2716,7 +2706,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2726,7 +2716,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2753,10 +2743,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122969601</v>
+        <v>122969836</v>
       </c>
       <c r="B21" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2789,17 +2779,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481528</v>
+        <v>481538</v>
       </c>
       <c r="R21" t="n">
-        <v>6790490</v>
+        <v>6790506</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2826,9 +2816,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2843,22 +2843,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122971770</v>
+        <v>122970459</v>
       </c>
       <c r="B22" t="n">
-        <v>78799</v>
+        <v>57503</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2867,41 +2867,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481677</v>
+        <v>481658</v>
       </c>
       <c r="R22" t="n">
-        <v>6790565</v>
+        <v>6790493</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2928,19 +2928,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:53</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Miljöbilder och spillkråka.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2955,22 +2950,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122971698</v>
+        <v>122972025</v>
       </c>
       <c r="B23" t="n">
-        <v>8441</v>
+        <v>8445</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3001,19 +2996,24 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481661</v>
+        <v>481687</v>
       </c>
       <c r="R23" t="n">
-        <v>6790503</v>
+        <v>6790643</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3040,9 +3040,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3057,22 +3067,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122972843</v>
+        <v>122971698</v>
       </c>
       <c r="B24" t="n">
-        <v>78775</v>
+        <v>8445</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3081,38 +3091,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481748</v>
+        <v>481661</v>
       </c>
       <c r="R24" t="n">
-        <v>6790465</v>
+        <v>6790503</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3171,10 +3181,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122972025</v>
+        <v>122972089</v>
       </c>
       <c r="B25" t="n">
-        <v>8441</v>
+        <v>78781</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3183,43 +3193,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481687</v>
+        <v>481695</v>
       </c>
       <c r="R25" t="n">
-        <v>6790643</v>
+        <v>6790593</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3251,7 +3256,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3261,7 +3266,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3291,7 +3296,7 @@
         <v>122971852</v>
       </c>
       <c r="B26" t="n">
-        <v>8441</v>
+        <v>8445</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3405,10 +3410,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122972089</v>
+        <v>122972843</v>
       </c>
       <c r="B27" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3441,17 +3446,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481695</v>
+        <v>481748</v>
       </c>
       <c r="R27" t="n">
-        <v>6790593</v>
+        <v>6790465</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3478,19 +3483,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>15:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3505,22 +3500,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122970459</v>
+        <v>122971431</v>
       </c>
       <c r="B28" t="n">
-        <v>57497</v>
+        <v>78517</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3533,37 +3528,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
         <v>481658</v>
       </c>
       <c r="R28" t="n">
-        <v>6790493</v>
+        <v>6790494</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3590,14 +3585,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Miljöbilder och spillkråka.</t>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3612,22 +3612,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122972148</v>
+        <v>122973048</v>
       </c>
       <c r="B29" t="n">
-        <v>78776</v>
+        <v>8445</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3636,25 +3636,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>230405</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3664,10 +3664,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481755</v>
+        <v>481694</v>
       </c>
       <c r="R29" t="n">
-        <v>6790500</v>
+        <v>6790479</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Garnlav med miljöbild.</t>
+          <t>Mindre märgborre på låga.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3731,10 +3731,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122971431</v>
+        <v>122972148</v>
       </c>
       <c r="B30" t="n">
-        <v>78511</v>
+        <v>78782</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3747,37 +3747,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>230405</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481658</v>
+        <v>481755</v>
       </c>
       <c r="R30" t="n">
-        <v>6790494</v>
+        <v>6790500</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3804,19 +3804,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:44</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3831,22 +3826,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122973048</v>
+        <v>122971770</v>
       </c>
       <c r="B31" t="n">
-        <v>8441</v>
+        <v>78805</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3859,37 +3854,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6434</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481694</v>
+        <v>481677</v>
       </c>
       <c r="R31" t="n">
-        <v>6790479</v>
+        <v>6790565</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3916,14 +3911,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Mindre märgborre på låga.</t>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3938,12 +3938,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 33841-2023 artfynd.xlsx
+++ b/artfynd/A 33841-2023 artfynd.xlsx
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122969848</v>
+        <v>122970211</v>
       </c>
       <c r="B10" t="n">
-        <v>78782</v>
+        <v>78781</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,16 +1557,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1577,17 +1577,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481544</v>
+        <v>481559</v>
       </c>
       <c r="R10" t="n">
-        <v>6790494</v>
+        <v>6790521</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1614,14 +1614,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Torraka i bakgrunden.</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1636,19 +1641,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122970211</v>
+        <v>122969887</v>
       </c>
       <c r="B11" t="n">
         <v>78781</v>
@@ -1688,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481559</v>
+        <v>481534</v>
       </c>
       <c r="R11" t="n">
-        <v>6790521</v>
+        <v>6790501</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1723,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1738,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,7 +1765,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122969887</v>
+        <v>122970352</v>
       </c>
       <c r="B12" t="n">
         <v>78781</v>
@@ -1800,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481534</v>
+        <v>481566</v>
       </c>
       <c r="R12" t="n">
-        <v>6790501</v>
+        <v>6790511</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -1835,7 +1840,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1850,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122970352</v>
+        <v>122969848</v>
       </c>
       <c r="B13" t="n">
-        <v>78781</v>
+        <v>78782</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,16 +1893,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1908,17 +1913,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481566</v>
+        <v>481544</v>
       </c>
       <c r="R13" t="n">
-        <v>6790511</v>
+        <v>6790494</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1945,19 +1950,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:14</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Torraka i bakgrunden.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,12 +1972,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 33841-2023 artfynd.xlsx
+++ b/artfynd/A 33841-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122973404</v>
+        <v>122969543</v>
       </c>
       <c r="B2" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -711,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481525</v>
+        <v>481496</v>
       </c>
       <c r="R2" t="n">
-        <v>6790521</v>
+        <v>6790486</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Miljöbilder och garnlav.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,19 +777,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122973297</v>
+        <v>122969601</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -813,14 +808,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481575</v>
+        <v>481528</v>
       </c>
       <c r="R3" t="n">
-        <v>6790530</v>
+        <v>6790490</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,19 +874,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122969601</v>
+        <v>122969836</v>
       </c>
       <c r="B4" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -915,17 +905,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481528</v>
+        <v>481538</v>
       </c>
       <c r="R4" t="n">
-        <v>6790490</v>
+        <v>6790506</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -952,9 +942,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,31 +969,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122970062</v>
+        <v>122969887</v>
       </c>
       <c r="B5" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1021,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481533</v>
+        <v>481534</v>
       </c>
       <c r="R5" t="n">
-        <v>6790513</v>
+        <v>6790501</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1056,7 +1051,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1066,7 +1061,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,55 +1088,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122970166</v>
+        <v>122970062</v>
       </c>
       <c r="B6" t="n">
-        <v>8445</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481546</v>
+        <v>481533</v>
       </c>
       <c r="R6" t="n">
-        <v>6790501</v>
+        <v>6790513</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1173,7 +1158,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1168,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,19 +1195,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122970333</v>
+        <v>122970152</v>
       </c>
       <c r="B7" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1250,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481622</v>
+        <v>481577</v>
       </c>
       <c r="R7" t="n">
-        <v>6790484</v>
+        <v>6790481</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Garnlav med miljöbilder.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,19 +1292,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122973389</v>
+        <v>122970156</v>
       </c>
       <c r="B8" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1357,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481565</v>
+        <v>481546</v>
       </c>
       <c r="R8" t="n">
-        <v>6790545</v>
+        <v>6790501</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1392,7 +1362,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,7 +1372,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,19 +1399,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122973371</v>
+        <v>122970196</v>
       </c>
       <c r="B9" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1465,17 +1430,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481551</v>
+        <v>481598</v>
       </c>
       <c r="R9" t="n">
-        <v>6790539</v>
+        <v>6790481</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1502,19 +1467,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,12 +1484,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1544,16 +1499,11 @@
         <v>122970211</v>
       </c>
       <c r="B10" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1653,19 +1603,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122969887</v>
+        <v>122970333</v>
       </c>
       <c r="B11" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1689,17 +1634,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481534</v>
+        <v>481622</v>
       </c>
       <c r="R11" t="n">
-        <v>6790501</v>
+        <v>6790484</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1726,19 +1671,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:01</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbilder.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,12 +1693,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1768,16 +1708,11 @@
         <v>122970352</v>
       </c>
       <c r="B12" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1877,32 +1812,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122969848</v>
+        <v>122972089</v>
       </c>
       <c r="B13" t="n">
-        <v>78782</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1913,17 +1843,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481544</v>
+        <v>481695</v>
       </c>
       <c r="R13" t="n">
-        <v>6790494</v>
+        <v>6790593</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1950,14 +1880,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Torraka i bakgrunden.</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,31 +1907,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122973309</v>
+        <v>122972633</v>
       </c>
       <c r="B14" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2020,17 +1950,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481568</v>
+        <v>481748</v>
       </c>
       <c r="R14" t="n">
-        <v>6790545</v>
+        <v>6790465</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2057,19 +1987,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,31 +2004,26 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122970196</v>
+        <v>122973297</v>
       </c>
       <c r="B15" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2132,14 +2047,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481598</v>
+        <v>481575</v>
       </c>
       <c r="R15" t="n">
-        <v>6790481</v>
+        <v>6790530</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2198,19 +2113,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122970156</v>
+        <v>122973309</v>
       </c>
       <c r="B16" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2238,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481546</v>
+        <v>481568</v>
       </c>
       <c r="R16" t="n">
-        <v>6790501</v>
+        <v>6790545</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2273,7 +2183,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2193,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,19 +2220,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122970152</v>
+        <v>122973371</v>
       </c>
       <c r="B17" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2346,17 +2251,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481577</v>
+        <v>481551</v>
       </c>
       <c r="R17" t="n">
-        <v>6790481</v>
+        <v>6790539</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2383,9 +2288,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2400,49 +2315,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122970092</v>
+        <v>122973389</v>
       </c>
       <c r="B18" t="n">
-        <v>78805</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2452,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481532</v>
+        <v>481565</v>
       </c>
       <c r="R18" t="n">
-        <v>6790516</v>
+        <v>6790545</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2487,7 +2397,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2497,7 +2407,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2524,32 +2434,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122969981</v>
+        <v>122973404</v>
       </c>
       <c r="B19" t="n">
-        <v>78782</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2560,14 +2465,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481565</v>
+        <v>481525</v>
       </c>
       <c r="R19" t="n">
-        <v>6790484</v>
+        <v>6790521</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2600,11 +2505,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Garnlav runt omkring mig i en radie av 40 meter.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2634,12 +2534,7 @@
         <v>122969800</v>
       </c>
       <c r="B20" t="n">
-        <v>78805</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2743,37 +2638,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122969836</v>
+        <v>122970092</v>
       </c>
       <c r="B21" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2783,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481538</v>
+        <v>481532</v>
       </c>
       <c r="R21" t="n">
-        <v>6790506</v>
+        <v>6790516</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -2818,7 +2708,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2828,7 +2718,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,53 +2745,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122970459</v>
+        <v>122971770</v>
       </c>
       <c r="B22" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hedsvasseln, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481658</v>
+        <v>481677</v>
       </c>
       <c r="R22" t="n">
-        <v>6790493</v>
+        <v>6790565</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2928,14 +2813,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Miljöbilder och spillkråka.</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2950,67 +2840,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122972025</v>
+        <v>122971431</v>
       </c>
       <c r="B23" t="n">
-        <v>8445</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481687</v>
+        <v>481658</v>
       </c>
       <c r="R23" t="n">
-        <v>6790643</v>
+        <v>6790494</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3042,7 +2922,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3052,7 +2932,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3079,15 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122971698</v>
+        <v>122970459</v>
       </c>
       <c r="B24" t="n">
-        <v>8445</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3095,21 +2970,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3119,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481661</v>
+        <v>481658</v>
       </c>
       <c r="R24" t="n">
-        <v>6790503</v>
+        <v>6790493</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3155,6 +3030,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Miljöbilder och spillkråka.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3181,50 +3061,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122972089</v>
+        <v>122970166</v>
       </c>
       <c r="B25" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481695</v>
+        <v>481546</v>
       </c>
       <c r="R25" t="n">
-        <v>6790593</v>
+        <v>6790501</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3256,7 +3136,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3266,7 +3146,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3293,15 +3173,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122971852</v>
+        <v>122971698</v>
       </c>
       <c r="B26" t="n">
-        <v>8445</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3327,24 +3202,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481678</v>
+        <v>481661</v>
       </c>
       <c r="R26" t="n">
-        <v>6790570</v>
+        <v>6790503</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3371,19 +3241,9 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3398,65 +3258,65 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122972843</v>
+        <v>122971852</v>
       </c>
       <c r="B27" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481748</v>
+        <v>481678</v>
       </c>
       <c r="R27" t="n">
-        <v>6790465</v>
+        <v>6790570</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3483,9 +3343,19 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3500,62 +3370,62 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122971431</v>
+        <v>122972025</v>
       </c>
       <c r="B28" t="n">
-        <v>78517</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Höghedsberget, Höghedsberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481658</v>
+        <v>481687</v>
       </c>
       <c r="R28" t="n">
-        <v>6790494</v>
+        <v>6790643</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -3587,7 +3457,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3597,7 +3467,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3627,12 +3497,7 @@
         <v>122973048</v>
       </c>
       <c r="B29" t="n">
-        <v>8445</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3731,19 +3596,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122972148</v>
+        <v>122969848</v>
       </c>
       <c r="B30" t="n">
-        <v>78782</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3767,14 +3627,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481755</v>
+        <v>481544</v>
       </c>
       <c r="R30" t="n">
-        <v>6790500</v>
+        <v>6790494</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3811,7 +3671,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Garnlav med miljöbild.</t>
+          <t>Torraka i bakgrunden.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3838,53 +3698,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122971770</v>
+        <v>122969981</v>
       </c>
       <c r="B31" t="n">
-        <v>78805</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6434</v>
+        <v>230405</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Höghedsberget, Höghedsberget, Dlr</t>
+          <t>Hedsvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481677</v>
+        <v>481565</v>
       </c>
       <c r="R31" t="n">
-        <v>6790565</v>
+        <v>6790484</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3911,19 +3766,14 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:53</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Garnlav runt omkring mig i en radie av 40 meter.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3938,15 +3788,117 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>122972148</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Höghedsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>481755</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6790500</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Garnlav med miljöbild.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
